--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2718-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2718-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4699CA0A-75FD-44CE-A616-E1D0B2F7AA84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5FAC301D-6C7C-4FA5-895B-891163DD3CD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{775C8ECD-1BCE-4E67-8BE9-E4CD9A269996}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{1DCC1D5A-073E-4CC1-A49E-DE2EA17C6A42}"/>
   </bookViews>
   <sheets>
     <sheet name="2718-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1525,30 +1525,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D9325EC-4510-408D-8B1F-0DA1B1C5D94A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4295D41-AD53-4A70-92CA-1BBCFFFD1C1C}">
   <dimension ref="A1:X29"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.75" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -1582,7 +1582,7 @@
       <c r="W1" s="29"/>
       <c r="X1" s="21"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
@@ -1618,7 +1618,7 @@
       <c r="W2" s="31"/>
       <c r="X2" s="32"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="X3" s="35"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="24"/>
       <c r="B4" s="25"/>
       <c r="C4" s="7"/>
@@ -1738,7 +1738,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="36">
         <v>2025</v>
       </c>
@@ -1810,7 +1810,7 @@
         <v>6.94</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="38"/>
       <c r="B6" s="39"/>
       <c r="C6" s="41"/>
@@ -1846,7 +1846,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>30</v>
       </c>
@@ -1920,7 +1920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>30</v>
       </c>
@@ -1994,7 +1994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>30</v>
       </c>
@@ -2068,7 +2068,7 @@
         <v>3.47</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="46">
         <v>2024</v>
       </c>
@@ -2140,7 +2140,7 @@
         <v>6.97</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="48">
         <v>2023</v>
       </c>
@@ -2212,7 +2212,7 @@
         <v>5.81</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="46">
         <v>2022</v>
       </c>
@@ -2284,7 +2284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="48">
         <v>2021</v>
       </c>
@@ -2356,7 +2356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="46">
         <v>2020</v>
       </c>
@@ -2428,7 +2428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="48">
         <v>2019</v>
       </c>
@@ -2500,7 +2500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="46">
         <v>2018</v>
       </c>
@@ -2572,7 +2572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="48">
         <v>2017</v>
       </c>
@@ -2644,7 +2644,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="46">
         <v>2016</v>
       </c>
@@ -2716,7 +2716,7 @@
         <v>2.5099999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="48">
         <v>2015</v>
       </c>
@@ -2788,7 +2788,7 @@
         <v>2.78</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="46">
         <v>2014</v>
       </c>
@@ -2860,7 +2860,7 @@
         <v>1.66</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="48">
         <v>2013</v>
       </c>
@@ -2932,7 +2932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="46">
         <v>2012</v>
       </c>
@@ -3004,7 +3004,7 @@
         <v>2.41</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="48">
         <v>2011</v>
       </c>
@@ -3076,7 +3076,7 @@
         <v>4.2300000000000004</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="46">
         <v>2010</v>
       </c>
@@ -3148,7 +3148,7 @@
         <v>2.4900000000000002</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="48">
         <v>2009</v>
       </c>
@@ -3220,7 +3220,7 @@
         <v>3.04</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="46">
         <v>2008</v>
       </c>
@@ -3292,7 +3292,7 @@
         <v>6.27</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="48">
         <v>2007</v>
       </c>
@@ -3364,7 +3364,7 @@
         <v>5.22</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="16" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="16" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="46">
         <v>2006</v>
       </c>
@@ -3436,7 +3436,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="48" t="s">
         <v>49</v>
       </c>
